--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.10608968995065</v>
+        <v>8.954739574616982</v>
       </c>
       <c r="D2" t="n">
-        <v>55.2684429679167</v>
+        <v>8.981121982286464</v>
       </c>
       <c r="E2" t="n">
-        <v>18.80708973243516</v>
+        <v>3.056152081520713</v>
       </c>
       <c r="F2" t="n">
-        <v>18.78513395962245</v>
+        <v>3.052584268438648</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>92.72026915482097</v>
+        <v>15.06704373765841</v>
       </c>
       <c r="D3" t="n">
-        <v>92.8387108871616</v>
+        <v>15.08629051916376</v>
       </c>
       <c r="E3" t="n">
-        <v>18.80708973243516</v>
+        <v>3.056152081520713</v>
       </c>
       <c r="F3" t="n">
-        <v>18.78513395962245</v>
+        <v>3.052584268438648</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
